--- a/tests/testdata/excel/多数シート.xlsx
+++ b/tests/testdata/excel/多数シート.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\test\AppData\Local\Temp\win_grep_testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EFB2CB9A-EB11-47DB-A301-7AE036FC7465}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3EAED238-FE63-4970-9AB9-4BDAB4725684}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="10515" xr2:uid="{2F20332F-ECBF-41D0-B9A3-E4C4DBDCA145}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{15F0F959-E216-4394-A7D9-F6C6BE4096D0}"/>
   </bookViews>
   <sheets>
     <sheet name="S01" sheetId="1" r:id="rId1"/>
@@ -663,7 +663,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{940B1B33-8343-4D77-A548-3FDF87532F72}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42B127B8-85CB-4488-A853-0C516335DAD0}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -682,7 +682,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65C404FF-0D4A-441C-8F82-DAF7DC3DD52C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1A78326-8621-4276-8824-E918E6D71976}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -701,7 +701,7 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{380AD376-85FD-497D-8FDD-C43F72ACC7BB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F7D36C4-8396-477A-B89F-4DC73BE6F076}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -720,7 +720,7 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFF7CBF3-F857-47F4-8B11-86474AFFE492}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1AB11EE-E640-40A3-B638-77EDF44311ED}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -739,7 +739,7 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A543ADA-0EEB-4402-9A69-85A767F5DD0D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{416FE69C-E3D4-41FF-B15A-0CD7221B1068}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -758,7 +758,7 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23231122-BCBC-4914-BF71-44E606198086}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A4BE217-29A5-4638-BD5C-194CD99037A4}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -777,7 +777,7 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C57DE3E4-0783-4074-9422-ADEABB1B144D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06D8E1F0-1B44-4A8D-B7CE-17E04D0C1A35}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -796,7 +796,7 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9324EBE-56FD-4DCB-B971-7C558220B4F5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C379364C-A8D3-4931-B84E-50B8BA609A52}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -815,7 +815,7 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BC2D72C-226C-42E4-A0E3-98B8AE3F1B05}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{240688D7-9B6C-4C49-874A-4C4510D378AE}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -834,7 +834,7 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7FD7024-1D57-4F76-8825-BAE734C14CD9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64A40540-3F46-4E64-AB92-0DB195BB5D97}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -853,7 +853,7 @@
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF0504BC-85C6-4997-8BA7-8428B8DAC08C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB406BF1-7045-4C60-B578-826EBD875D78}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -872,7 +872,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F54EB1E5-D21E-455C-8552-7D89354FFA22}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D92ED60-438D-4B7E-8A0A-0F8D41DBF6D2}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -891,7 +891,7 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3211E075-0A95-4504-8EF0-E6336E3E520C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C488AC6-E0AB-4CE3-AC39-808A05E6A5AD}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -910,7 +910,7 @@
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44C7E501-DD9B-48D3-9B2E-43457103D93F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCA654C1-00E4-4A08-BD39-40C04195E5C7}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -929,7 +929,7 @@
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6857F4CD-8D6D-437A-B7E5-D35A3180A839}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B31BDE09-406F-4DC1-BBDB-4904D6819E4E}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -948,7 +948,7 @@
 </file>
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D748071E-E790-4DC8-886F-FAAB9A2EBE34}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F823CB4D-7AC1-40A0-AA41-A1507C8F72C6}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -967,7 +967,7 @@
 </file>
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56235BD1-5B28-4800-962A-82270109DF83}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2548DFB-EEE2-42C6-A843-D60E79008C6E}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -986,7 +986,7 @@
 </file>
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CF9B902-0BE8-4A81-9709-AE1324327E74}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA171548-D63F-4662-A34C-44557FCB0321}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1005,7 +1005,7 @@
 </file>
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A73E4B2-A474-40E5-B4FC-9E0AE60C6ED4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E40ED6A-0972-4CC3-B738-348742354207}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1024,7 +1024,7 @@
 </file>
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99BF239C-AD49-4EE5-9C37-4BB04EDEC1ED}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA1D4676-54A3-4E17-8783-5DBEAD8E9E47}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1043,7 +1043,7 @@
 </file>
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{272EDB6B-2682-40D4-87BD-B68E2C99079A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBAA7CB7-4C9D-48BF-BF9A-98E72F6E68B1}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1062,7 +1062,7 @@
 </file>
 
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32E04EB6-B5BC-4C32-92FC-4662AA20CB6D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAFC1B54-FEDB-45DF-BF59-B2C4E03D1EC7}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1081,7 +1081,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA16C232-7843-4BF7-B4D8-2B9987BD364F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32DF0465-4A73-4395-B7BE-50DA39E5E25F}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1100,7 +1100,7 @@
 </file>
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85AFC62F-7D73-4267-80B9-CC936F1FD169}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B9A3DA5-793D-4AD8-A162-8A5EADDF30F9}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1119,7 +1119,7 @@
 </file>
 
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EA1FF46-2E67-49BC-884F-D231FD39CBAE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11F9EBE6-9440-43BF-A257-F06E12F80D73}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1138,7 +1138,7 @@
 </file>
 
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3B3BED1-5D26-4D93-A3F2-40B67CA93BC6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{819397D5-6CF8-414A-B941-7A9FB83EAEA3}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1157,7 +1157,7 @@
 </file>
 
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F94D8CFB-AEF8-4442-BC48-55C3752E5C06}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6DE169D-71D4-4F8A-B9EC-D69992DEE7AF}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1176,7 +1176,7 @@
 </file>
 
 <file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97AA0C83-2A8C-4F50-96AB-5AB76ED654C2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FAEFDEB-FDFC-4D18-B5B6-5F968C71E431}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1195,7 +1195,7 @@
 </file>
 
 <file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56F5FD15-A499-420C-82B8-E79248C5BA67}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E07D1D89-25C8-404E-8505-2F46F989A407}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1214,7 +1214,7 @@
 </file>
 
 <file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{622D56AB-7ECD-40AB-A106-AEA2966B5156}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFA9A00A-2B04-4227-903D-5B1BB56A3960}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1233,7 +1233,7 @@
 </file>
 
 <file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71150A9A-D01C-4E3F-B33A-E38D0C9B32E2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3F3D39E-DF3A-4574-90BD-AED4C5800183}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1252,7 +1252,7 @@
 </file>
 
 <file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DE7B321-00A9-4DD9-8B74-D468EA2AE0EB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27D81594-A902-459E-B01D-003A03A3EA63}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1271,7 +1271,7 @@
 </file>
 
 <file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ABCB216D-EEF3-496D-BB7C-D7D649580F18}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3033B71C-DF48-45B3-A1DD-651547C93037}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1290,7 +1290,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{800DFCB9-64F6-4E30-B95F-98EE77C3BD22}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37D08EC2-8710-4695-B4A9-A08A5AD1FC74}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1309,7 +1309,7 @@
 </file>
 
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48AC032A-83F7-4FB1-B4A5-B434BCEB3ADD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA0B07EE-A9D2-4E29-BE44-6B009EB0DE2D}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1328,7 +1328,7 @@
 </file>
 
 <file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D6AE329-40EE-4C60-9B5F-24533324D603}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2658A31-8562-47B7-A7B6-9ECE151FBDEA}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1347,7 +1347,7 @@
 </file>
 
 <file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1133FB6-B3A5-4DBA-8F88-EA31CAF2FEBC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A53FB9F-D1EF-43C5-9875-5F049AAD584F}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1366,7 +1366,7 @@
 </file>
 
 <file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A62FC44-D1A2-47B4-A9B1-BF95C042DAFD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CC092B9-C7BC-467D-97AA-22B5E3D361A5}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1385,7 +1385,7 @@
 </file>
 
 <file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06FAAB84-9D92-46E7-9C32-FAA548051AC9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E274DBA8-AE00-437A-9CDD-1BC2090D57BA}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1404,7 +1404,7 @@
 </file>
 
 <file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CFE674D-EFCB-4E0D-AA52-B1EF633CFE51}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08A7E1C8-F4C8-480D-AA39-F3C12F5D57B2}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1423,7 +1423,7 @@
 </file>
 
 <file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6084C034-26F4-421C-85FE-4A2247E33F72}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75E18BC5-A26C-42AD-98FD-5752B27A42A4}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1442,7 +1442,7 @@
 </file>
 
 <file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F8D8C5B-196B-434A-893D-9F0D9AF13601}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{228352AD-7529-4BA9-BA77-EE65F30AFCD6}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1461,7 +1461,7 @@
 </file>
 
 <file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CC3A04D-92D7-45F5-B76F-97B44B2B395C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33DF15F4-7373-49EA-AC7D-7C73387DD048}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1480,7 +1480,7 @@
 </file>
 
 <file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEBC5E95-7771-4102-A3C8-02F4F1B046B1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{683855E5-4AFF-48B5-A347-F9616E97BE3C}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1499,7 +1499,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94AE0BF7-0B32-4335-82E2-3E9653573652}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{248D50C1-B016-4B29-8F89-585698D5DE2B}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1518,7 +1518,7 @@
 </file>
 
 <file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB5A735A-07FF-4C0D-A690-17C292E3D5EC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97FAE4C9-EEF0-48EF-99E4-791685DACDB8}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1537,7 +1537,7 @@
 </file>
 
 <file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE782D18-ACFA-43FA-9416-5C4898D55C44}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7633213A-C94D-4319-978A-7E5A9E04BE45}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1556,7 +1556,7 @@
 </file>
 
 <file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90F5DBEE-DBBC-42B7-9C11-7563826788D3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A76AEBA-1E37-405E-9BB4-6F54A9435425}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1575,7 +1575,7 @@
 </file>
 
 <file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BF66136-D1C2-4538-BE5A-B0E4C43CFC7C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DE2EF6E-4309-468D-BF0D-08D4B370EEA7}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1594,7 +1594,7 @@
 </file>
 
 <file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2E27106-A194-476F-9C38-EC30F9B6E48B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A50CACCA-57BF-49AB-B3CE-B05CE94DBFCA}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1613,7 +1613,7 @@
 </file>
 
 <file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B85DD2B-268C-4750-B97F-9B786DF4EB14}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FB0FC56-AD0F-438D-A7B5-9E18DE820D3A}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1632,7 +1632,7 @@
 </file>
 
 <file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B094D2F5-299C-407C-A0E5-6C46CCCA79D7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{464E77F6-9E2A-44E5-8A36-81EF92D0CB8D}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1651,7 +1651,7 @@
 </file>
 
 <file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D79A5BE6-62AF-40C1-88EC-3AA2494F1327}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B0D3F0B-7602-41C6-A562-8DA87EE173DC}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1670,7 +1670,7 @@
 </file>
 
 <file path=xl/worksheets/sheet58.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5AD4D608-03CF-4094-B18A-E49BE94C3A86}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB322848-AA90-473A-B600-0544143E8118}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1689,7 +1689,7 @@
 </file>
 
 <file path=xl/worksheets/sheet59.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CA628E9-B9EE-469B-A65B-7E7476899598}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DDFD78F-4F39-4C85-8E16-D595942E44BB}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1708,7 +1708,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D64D0772-2F2E-4BAE-BECB-7CE1ABC77726}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADB6C408-A78C-4ECE-8D7C-63E07DC518EE}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1727,7 +1727,7 @@
 </file>
 
 <file path=xl/worksheets/sheet60.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6D4D673-FA85-4F45-B5E3-74B75B26F34F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DE46771-C26A-4350-81C3-61BDCD1FA009}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1746,7 +1746,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{695882C3-CF7F-46B6-B3E7-DB4F1CA877EE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CD21829-1DA5-4CF8-BF2F-B3B1C0A2EF21}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1765,7 +1765,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64202AB9-E38B-4707-9904-7F17F66A01B0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7ED9F705-BC37-4C64-A8F4-2CE7C9D33ACC}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1784,7 +1784,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2198410-957E-48A8-AD68-C4A1E9A1C409}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4773CB14-8503-4687-8F89-8EC436B6768D}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>

--- a/tests/testdata/excel/多数シート.xlsx
+++ b/tests/testdata/excel/多数シート.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\test\AppData\Local\Temp\win_grep_testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3EAED238-FE63-4970-9AB9-4BDAB4725684}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B3DB1D48-23C4-4749-9747-B66A480C9B76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{15F0F959-E216-4394-A7D9-F6C6BE4096D0}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{01C8176A-AC2B-4D50-9E44-F14DC25B68BF}"/>
   </bookViews>
   <sheets>
     <sheet name="S01" sheetId="1" r:id="rId1"/>
@@ -663,7 +663,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42B127B8-85CB-4488-A853-0C516335DAD0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C705637-F0EC-4336-A705-DCDFA61CE8AB}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -682,7 +682,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1A78326-8621-4276-8824-E918E6D71976}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D949AE83-3419-4CC6-B22B-50D45679621C}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -701,7 +701,7 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F7D36C4-8396-477A-B89F-4DC73BE6F076}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C72F572-4118-444E-9FE1-7CE2D91973A5}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -720,7 +720,7 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1AB11EE-E640-40A3-B638-77EDF44311ED}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B4AB791-80B8-42C6-BAFC-16CD4EE88BAC}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -739,7 +739,7 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{416FE69C-E3D4-41FF-B15A-0CD7221B1068}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98AFBC80-8EE3-4F59-9DA3-AE3B6A6169B7}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -758,7 +758,7 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A4BE217-29A5-4638-BD5C-194CD99037A4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74EDB04E-D59E-4F10-8502-112F99E929A7}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -777,7 +777,7 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06D8E1F0-1B44-4A8D-B7CE-17E04D0C1A35}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEE3DC7F-82A8-42F4-B9E2-84464A7ACD8E}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -796,7 +796,7 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C379364C-A8D3-4931-B84E-50B8BA609A52}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39058F5D-3DA1-4E27-8A76-1906237DA37C}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -815,7 +815,7 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{240688D7-9B6C-4C49-874A-4C4510D378AE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E5BC364-2C4F-473B-90D8-34B3711A236B}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -834,7 +834,7 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64A40540-3F46-4E64-AB92-0DB195BB5D97}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81D69DA2-5541-4ECF-8785-A3C04347B7DF}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -853,7 +853,7 @@
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB406BF1-7045-4C60-B578-826EBD875D78}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{485BE294-F6D8-4354-8DA8-7A54CF5D4272}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -872,7 +872,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D92ED60-438D-4B7E-8A0A-0F8D41DBF6D2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CED5DC4-0711-43E2-9C8E-433D832EF977}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -891,7 +891,7 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C488AC6-E0AB-4CE3-AC39-808A05E6A5AD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26362843-3345-4E69-BB3A-93617BBF5E78}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -910,7 +910,7 @@
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCA654C1-00E4-4A08-BD39-40C04195E5C7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26FA41A1-26E4-429B-81F3-003FCBDAB622}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -929,7 +929,7 @@
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B31BDE09-406F-4DC1-BBDB-4904D6819E4E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84CFCF80-F079-4554-97CA-66505E1CD6B8}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -948,7 +948,7 @@
 </file>
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F823CB4D-7AC1-40A0-AA41-A1507C8F72C6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00971D36-49C1-4D16-BF42-8BCFA4F9D873}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -967,7 +967,7 @@
 </file>
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2548DFB-EEE2-42C6-A843-D60E79008C6E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0C6F1B4-DBBE-4151-AFF6-83D8DDF90D61}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -986,7 +986,7 @@
 </file>
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA171548-D63F-4662-A34C-44557FCB0321}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5E7681D-A4D9-4486-8FA6-483CBACEF8CE}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1005,7 +1005,7 @@
 </file>
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E40ED6A-0972-4CC3-B738-348742354207}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2416C885-15D5-4281-9189-65D37DA8E7D3}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1024,7 +1024,7 @@
 </file>
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA1D4676-54A3-4E17-8783-5DBEAD8E9E47}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A282874-8CF7-4B50-9572-33097C60548A}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1043,7 +1043,7 @@
 </file>
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBAA7CB7-4C9D-48BF-BF9A-98E72F6E68B1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DD7732C-3352-4046-8061-E782C49BB6C5}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1062,7 +1062,7 @@
 </file>
 
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAFC1B54-FEDB-45DF-BF59-B2C4E03D1EC7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78124188-DBE3-4882-B9F0-5C5B8F75EE1E}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1081,7 +1081,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32DF0465-4A73-4395-B7BE-50DA39E5E25F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66E597FD-0C3E-4961-9E44-A00B1FB954C3}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1100,7 +1100,7 @@
 </file>
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B9A3DA5-793D-4AD8-A162-8A5EADDF30F9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BE1A454-AADA-4394-AB58-2FED826BB842}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1119,7 +1119,7 @@
 </file>
 
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11F9EBE6-9440-43BF-A257-F06E12F80D73}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9657A6E3-8331-4963-BABB-B627D244C379}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1138,7 +1138,7 @@
 </file>
 
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{819397D5-6CF8-414A-B941-7A9FB83EAEA3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0D0F882-3AF4-4D71-9617-07DBFCB305AC}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1157,7 +1157,7 @@
 </file>
 
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6DE169D-71D4-4F8A-B9EC-D69992DEE7AF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FB6E222-7610-4ABC-8E00-412FC80CC89C}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1176,7 +1176,7 @@
 </file>
 
 <file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FAEFDEB-FDFC-4D18-B5B6-5F968C71E431}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAC8AF0E-ACBF-46E2-B3F5-358F8074325C}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1195,7 +1195,7 @@
 </file>
 
 <file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E07D1D89-25C8-404E-8505-2F46F989A407}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E3C9B80-526C-4035-9A60-AE4A8A8640C3}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1214,7 +1214,7 @@
 </file>
 
 <file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFA9A00A-2B04-4227-903D-5B1BB56A3960}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{258783CC-2FBB-46A9-AB37-A6F3A4D430AE}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1233,7 +1233,7 @@
 </file>
 
 <file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3F3D39E-DF3A-4574-90BD-AED4C5800183}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEF6BD53-4CE0-4EC7-9B5C-3CDFA7B807BC}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1252,7 +1252,7 @@
 </file>
 
 <file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27D81594-A902-459E-B01D-003A03A3EA63}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E163AAB-2FDE-4E69-ACC9-B1F7D99CB6F3}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1271,7 +1271,7 @@
 </file>
 
 <file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3033B71C-DF48-45B3-A1DD-651547C93037}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{431B57E4-B589-47C0-BAA7-153F9571E046}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1290,7 +1290,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37D08EC2-8710-4695-B4A9-A08A5AD1FC74}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{391B3E6D-35AE-49B5-9C62-BBA8976A7247}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1309,7 +1309,7 @@
 </file>
 
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA0B07EE-A9D2-4E29-BE44-6B009EB0DE2D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF7B622D-B16D-4616-AB6B-5D27D8AF3803}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1328,7 +1328,7 @@
 </file>
 
 <file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2658A31-8562-47B7-A7B6-9ECE151FBDEA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CA30C8B-F033-41BF-A492-559EAFD2CADC}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1347,7 +1347,7 @@
 </file>
 
 <file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A53FB9F-D1EF-43C5-9875-5F049AAD584F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5965F43E-4EA6-4EC8-9EE3-16EDEC67A400}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1366,7 +1366,7 @@
 </file>
 
 <file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CC092B9-C7BC-467D-97AA-22B5E3D361A5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34FC62BF-8901-4E3C-97FE-F00DF7EFAABB}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1385,7 +1385,7 @@
 </file>
 
 <file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E274DBA8-AE00-437A-9CDD-1BC2090D57BA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{743EB81C-1F33-434F-ACA6-97BBC9AC15C9}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1404,7 +1404,7 @@
 </file>
 
 <file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08A7E1C8-F4C8-480D-AA39-F3C12F5D57B2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF5290C5-FDCF-41AB-8F85-D4F8774B302F}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1423,7 +1423,7 @@
 </file>
 
 <file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75E18BC5-A26C-42AD-98FD-5752B27A42A4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14BE46E3-7170-4B12-9F97-E28CD93F962A}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1442,7 +1442,7 @@
 </file>
 
 <file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{228352AD-7529-4BA9-BA77-EE65F30AFCD6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37DAAE95-0ABD-4D60-97D0-3D4A64EA9C1F}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1461,7 +1461,7 @@
 </file>
 
 <file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33DF15F4-7373-49EA-AC7D-7C73387DD048}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCA80C0B-F8F3-47F7-A57B-69BC20B48879}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1480,7 +1480,7 @@
 </file>
 
 <file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{683855E5-4AFF-48B5-A347-F9616E97BE3C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BB7D2CD-E9B3-4B7D-AC65-41A2ED8D0515}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1499,7 +1499,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{248D50C1-B016-4B29-8F89-585698D5DE2B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ABA1A30E-B147-4B75-928E-E61B4F4A0ED8}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1518,7 +1518,7 @@
 </file>
 
 <file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97FAE4C9-EEF0-48EF-99E4-791685DACDB8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D27A63E-5290-45E8-8C82-B9DC08A59427}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1537,7 +1537,7 @@
 </file>
 
 <file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7633213A-C94D-4319-978A-7E5A9E04BE45}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40C73F5A-6185-4DEF-AE72-108B2017E790}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1556,7 +1556,7 @@
 </file>
 
 <file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A76AEBA-1E37-405E-9BB4-6F54A9435425}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14D86CE2-5D4A-4AEC-8E5A-DCA63D70D430}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1575,7 +1575,7 @@
 </file>
 
 <file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DE2EF6E-4309-468D-BF0D-08D4B370EEA7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2FCCED8-D64E-403D-87CE-F76FE541A930}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1594,7 +1594,7 @@
 </file>
 
 <file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A50CACCA-57BF-49AB-B3CE-B05CE94DBFCA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05BE4F5A-4BB2-48F7-917A-88321355096D}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1613,7 +1613,7 @@
 </file>
 
 <file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FB0FC56-AD0F-438D-A7B5-9E18DE820D3A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49124CE2-D6B3-4811-A67A-69919AFF1966}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1632,7 +1632,7 @@
 </file>
 
 <file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{464E77F6-9E2A-44E5-8A36-81EF92D0CB8D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB55C836-B849-4E2A-8A32-EFAFD174F891}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1651,7 +1651,7 @@
 </file>
 
 <file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B0D3F0B-7602-41C6-A562-8DA87EE173DC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{251A3819-9A98-402C-91D6-D2B6194411D0}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1670,7 +1670,7 @@
 </file>
 
 <file path=xl/worksheets/sheet58.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB322848-AA90-473A-B600-0544143E8118}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A100834B-B69C-4795-BC78-2FA51AD606E9}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1689,7 +1689,7 @@
 </file>
 
 <file path=xl/worksheets/sheet59.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DDFD78F-4F39-4C85-8E16-D595942E44BB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AFE9D93-EA93-4219-A2E3-5D02CD698A18}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1708,7 +1708,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADB6C408-A78C-4ECE-8D7C-63E07DC518EE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEF854A7-B5C3-49BD-8B1D-042369A77763}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1727,7 +1727,7 @@
 </file>
 
 <file path=xl/worksheets/sheet60.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DE46771-C26A-4350-81C3-61BDCD1FA009}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3125C25-42A2-44DF-94E2-B89085374639}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1746,7 +1746,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CD21829-1DA5-4CF8-BF2F-B3B1C0A2EF21}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20878FAE-7176-4A70-8675-6442CFA88C25}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1765,7 +1765,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7ED9F705-BC37-4C64-A8F4-2CE7C9D33ACC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52F46C19-C4C5-4ABF-97AF-A3F4E8B00A60}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1784,7 +1784,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4773CB14-8503-4687-8F89-8EC436B6768D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCF512D0-6717-4347-849C-17985AA5D030}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
